--- a/out/S03_employee_training_feedback/agent3/agent3_test_cases_for_review.xlsx
+++ b/out/S03_employee_training_feedback/agent3/agent3_test_cases_for_review.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>DT1</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>DT1 | Great, you're eligible for this survey! Next, a few quick questions about your recent training session. | text display | — | Always show</t>
+          <t>Q1 | Which channel did you primarily use for this training session? | single | In person; Live virtual; Self-paced online | Always show</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -943,71 +943,15 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>TC-4e572a11b8</t>
+          <t>TC-611fbac190</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>DT1's wording comes from S1's answer: the earlier answer should appear in the wording</t>
+          <t>Prove the survey flows correctly at Q1: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>1. S1 = Yes
-2. S2 = Yes</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>After submitting S2, look for DT1 on the next page. Do not answer it.</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>1. DT1's wording includes the words: Yes</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>Wording carried forward</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Q1 | Which channel did you primarily use for this training session? | single | In person; Live virtual; Self-paced online | Always show</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>TC-611fbac190</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Prove the survey flows correctly at Q1: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -1020,20 +964,77 @@
 9. Q7 = 0</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>1. Q1 IS shown on the page
 2. the next question shown is Q2</t>
         </is>
       </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Shows / hides correctly</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Q1 | Which channel did you primarily use for this training session? | single | In person; Live virtual; Self-paced online | Always show</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>TC-867b163807</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Prove Q1 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Yes</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>At Q1, select nothing at all, then submit.</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q1</t>
+        </is>
+      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Shows / hides correctly</t>
+          <t>Blank answer is blocked</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1048,12 +1049,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Q1 | Which channel did you primarily use for this training session? | single | In person; Live virtual; Self-paced online | Always show</t>
+          <t>Q2 | Overall, how satisfied were you with the training session? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1063,128 +1064,15 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>TC-867b163807</t>
+          <t>TC-86937a6bf5</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Prove Q1 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
+          <t>Prove the survey flows correctly at Q2: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>1. S1 = Yes
-2. S2 = Yes</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>At Q1, select nothing at all, then submit.</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q1</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>Blank answer is blocked</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Q1 | Which channel did you primarily use for this training session? | single | In person; Live virtual; Self-paced online | Always show</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>TC-e713ebe920</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Q1's wording comes from S1's answer: the earlier answer should appear in the wording</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>1. S1 = Yes
-2. S2 = Yes</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>At Q1, choose “In person”, then submit.</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>1. Q1's wording includes the words: Yes</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>Wording carried forward</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Q2 | Overall, how satisfied were you with the training session? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>TC-86937a6bf5</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Prove the survey flows correctly at Q2: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -1197,173 +1085,116 @@
 9. Q7 = 0</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>1. Q2 IS shown on the page
 2. the next question shown is Q3</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Q2 | Overall, how satisfied were you with the training session? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>TC-d9f680202c</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>Prove Q2 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
 3. Q1 = In person</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>At Q2, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q2</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Q2 | Overall, how satisfied were you with the training session? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>TC-d2c8555f25</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Q2's wording comes from S1's answer: the earlier answer should appear in the wording</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>1. S1 = Yes
-2. S2 = Yes
-3. Q1 = In person</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>At Q2, choose “Very poor”, then submit.</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>1. Q2's wording includes the words: Yes</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>Wording carried forward</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Q3 | How easy was it to complete what you wanted to do? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>TC-98e19afc55</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q3: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -1376,58 +1207,58 @@
 9. Q7 = 0</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>1. Q3 IS shown on the page
 2. the next question shown is Q4_SQ001</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Q3 | How easy was it to complete what you wanted to do? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>TC-3852293e7b</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>Prove Q3 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -1435,58 +1266,58 @@
 4. Q2 = Very poor</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>At Q3, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q3</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Q4 | Which aspects influenced your rating? Select all that apply. | multi | Content relevance; Instructor quality; Exercises; Pace; Materials; Technology | Validate: {"min_selections": 1}</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>TC-87faf5d4ed</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q4: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -1499,20 +1330,199 @@
 9. Q7 = 0</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>1. Q4 IS shown on the page
 2. the next question shown is Q5</t>
         </is>
       </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Shows / hides correctly</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Q4 | Which aspects influenced your rating? Select all that apply. | multi | Content relevance; Instructor quality; Exercises; Pace; Materials; Technology | Validate: {"min_selections": 1}</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>TC-0cf882fb0a</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Prove Q4 ACCEPTS an answer that obeys its rule. The QRE's rule is: at least 1 option must be selected</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Yes
+3. Q1 = In person
+4. Q2 = Very poor
+5. Q3 = Very poor</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>At Q4, tick 1 option (Content relevance), then submit.</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>1. the survey ACCEPTS the answer and moves to the next page</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Answer rule accepts or rejects</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Q4 | Which aspects influenced your rating? Select all that apply. | multi | Content relevance; Instructor quality; Exercises; Pace; Materials; Technology | Validate: {"min_selections": 1}</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>TC-301bb02157</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Prove Q4 REJECTS an answer that breaks its rule. The QRE's rule is: at least 1 option must be selected</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Yes
+3. Q1 = In person
+4. Q2 = Very poor
+5. Q3 = Very poor</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>At Q4, select nothing at all, then submit.</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q4</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Answer rule accepts or rejects</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Q4 | Which aspects influenced your rating? Select all that apply. | multi | Content relevance; Instructor quality; Exercises; Pace; Materials; Technology | Validate: {"min_selections": 1}</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>TC-83f4fded00</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Prove Q4 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a multi question  [Same actions as TC-301bb02157 on this question: the questionnaire's answer rule and its compulsory setting come down to the same thing here. Both are kept because they are separate claims, but one run satisfies both.]</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Yes
+3. Q1 = In person
+4. Q2 = Very poor
+5. Q3 = Very poor</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>At Q4, select nothing at all, then submit.</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q4</t>
+        </is>
+      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Shows / hides correctly</t>
+          <t>Blank answer is blocked</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1527,12 +1537,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Q4 | Which aspects influenced your rating? Select all that apply. | multi | Content relevance; Instructor quality; Exercises; Pace; Materials; Technology | Validate: {"min_selections": 1}</t>
+          <t>Q5 | Did you encounter a problem? | single | Yes; No | Always show</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1542,194 +1552,15 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>TC-0cf882fb0a</t>
+          <t>TC-5912a4b2c6</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Prove Q4 ACCEPTS an answer that obeys its rule. The QRE's rule is: at least 1 option must be selected</t>
+          <t>Prove the survey flows correctly at Q5: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>1. S1 = Yes
-2. S2 = Yes
-3. Q1 = In person
-4. Q2 = Very poor
-5. Q3 = Very poor</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>At Q4, tick 1 option (Content relevance), then submit.</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>1. the survey ACCEPTS the answer and moves to the next page</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>Answer rule accepts or rejects</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Q4</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Q4 | Which aspects influenced your rating? Select all that apply. | multi | Content relevance; Instructor quality; Exercises; Pace; Materials; Technology | Validate: {"min_selections": 1}</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>TC-301bb02157</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Prove Q4 REJECTS an answer that breaks its rule. The QRE's rule is: at least 1 option must be selected</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>1. S1 = Yes
-2. S2 = Yes
-3. Q1 = In person
-4. Q2 = Very poor
-5. Q3 = Very poor</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>At Q4, select nothing at all, then submit.</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q4</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>Answer rule accepts or rejects</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Q4</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Q4 | Which aspects influenced your rating? Select all that apply. | multi | Content relevance; Instructor quality; Exercises; Pace; Materials; Technology | Validate: {"min_selections": 1}</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>TC-83f4fded00</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>Prove Q4 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a multi question  [Same actions as TC-301bb02157 on this question: the questionnaire's answer rule and its compulsory setting come down to the same thing here. Both are kept because they are separate claims, but one run satisfies both.]</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>1. S1 = Yes
-2. S2 = Yes
-3. Q1 = In person
-4. Q2 = Very poor
-5. Q3 = Very poor</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>At Q4, select nothing at all, then submit.</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q4</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>Blank answer is blocked</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Q5</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Q5 | Did you encounter a problem? | single | Yes; No | Always show</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>TC-5912a4b2c6</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Prove the survey flows correctly at Q5: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -1742,20 +1573,201 @@
 9. Q7 = 0</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>1. Q5 IS shown on the page
 2. the next question shown is Q6</t>
         </is>
       </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Shows / hides correctly</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Q5 | Did you encounter a problem? | single | Yes; No | Always show</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>TC-3caa8e093d</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Rule R4: the jump should happen. Jump to Q7 when Q5 == 'No'</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Yes
+3. Q1 = In person
+4. Q2 = Very poor
+5. Q3 = Very poor
+6. Q4 = Content relevance</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>At Q5, choose “No”, then submit.</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>1. the next question shown is Q7</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Shows / hides correctly</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Q5 | Did you encounter a problem? | single | Yes; No | Always show</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>TC-7a43b34fce</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Rule R4: the jump should not happen. Jump to Q7 when Q5 == 'No'</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Yes
+3. Q1 = In person
+4. Q2 = Very poor
+5. Q3 = Very poor
+6. Q4 = Content relevance</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>At Q5, choose “Yes”, then submit.</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>1. the next question shown is Q6</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Shows / hides correctly</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Q5 | Did you encounter a problem? | single | Yes; No | Always show</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>TC-cb49dec5c7</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Prove Q5 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Yes
+3. Q1 = In person
+4. Q2 = Very poor
+5. Q3 = Very poor
+6. Q4 = Content relevance</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>At Q5, select nothing at all, then submit.</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q5</t>
+        </is>
+      </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Shows / hides correctly</t>
+          <t>Blank answer is blocked</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1770,212 +1782,31 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Q5 | Did you encounter a problem? | single | Yes; No | Always show</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>TC-3caa8e093d</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>Rule R4: the jump should happen. Jump to Q7 when Q5 == 'No'</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>1. S1 = Yes
-2. S2 = Yes
-3. Q1 = In person
-4. Q2 = Very poor
-5. Q3 = Very poor
-6. Q4 = Content relevance</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>At Q5, choose “No”, then submit.</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>1. the next question shown is Q7</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>Shows / hides correctly</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Q5</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Q5 | Did you encounter a problem? | single | Yes; No | Always show</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>TC-7a43b34fce</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Rule R4: the jump should not happen. Jump to Q7 when Q5 == 'No'</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>1. S1 = Yes
-2. S2 = Yes
-3. Q1 = In person
-4. Q2 = Very poor
-5. Q3 = Very poor
-6. Q4 = Content relevance</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>At Q5, choose “Yes”, then submit.</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>1. the next question shown is Q6</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>Shows / hides correctly</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Q5</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Q5 | Did you encounter a problem? | single | Yes; No | Always show</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>TC-cb49dec5c7</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>Prove Q5 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>1. S1 = Yes
-2. S2 = Yes
-3. Q1 = In person
-4. Q2 = Very poor
-5. Q3 = Very poor
-6. Q4 = Content relevance</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>At Q5, select nothing at all, then submit.</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q5</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>Blank answer is blocked</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>Q6 | Please describe the main problem. | text | — | Show if: Q5 == 'Yes'
 Validate: {"min_length": 10, "max_length": 500}</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>TC-01610144c6</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q6: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -1988,20 +1819,207 @@
 9. Q7 = 0</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>1. Q6 IS shown on the page
 2. the next question shown is Q7</t>
         </is>
       </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Shows / hides correctly</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Q6 | Please describe the main problem. | text | — | Show if: Q5 == 'Yes'
+Validate: {"min_length": 10, "max_length": 500}</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>TC-a0f36ff8a3</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Prove Q6 DOES appear when its condition is met. The QRE says show it if: Q5 == 'Yes'</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Yes
+3. Q1 = In person
+4. Q2 = Very poor
+5. Q3 = Very poor
+6. Q4 = Content relevance
+7. Q5 = Yes</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>At Q6, type “xxxxxxxxxx”, then submit.</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>1. Q6 IS shown on the page</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Shows / hides correctly</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Q6 | Please describe the main problem. | text | — | Show if: Q5 == 'Yes'
+Validate: {"min_length": 10, "max_length": 500}</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>TC-d6163f31ce</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Prove Q6 does NOT appear when its condition is not met. The QRE says show it if: Q5 == 'Yes'</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Yes
+3. Q1 = In person
+4. Q2 = Very poor
+5. Q3 = Very poor
+6. Q4 = Content relevance
+7. Q5 = No</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>After submitting Q5, look for Q6 on the next page. Do not answer it.</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>1. Q6 is NOT shown on the page
+2. the respondent carries on into the survey rather than being screened out or finished</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Shows / hides correctly</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Q6 | Please describe the main problem. | text | — | Show if: Q5 == 'Yes'
+Validate: {"min_length": 10, "max_length": 500}</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>TC-1381ffa1c7</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Prove Q6 ACCEPTS an answer that obeys its rule. The QRE's rule is: the answer must be at least 10 characters; the answer must be at most 500 characters</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Yes
+3. Q1 = In person
+4. Q2 = Very poor
+5. Q3 = Very poor
+6. Q4 = Content relevance
+7. Q5 = Yes</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>At Q6, type “xxxxxxxxxx”, then submit.</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>1. the survey ACCEPTS the answer and moves to the next page</t>
+        </is>
+      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Shows / hides correctly</t>
+          <t>Answer rule accepts or rejects</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2032,12 +2050,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>TC-a0f36ff8a3</t>
+          <t>TC-f70be2f9f4</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Prove Q6 DOES appear when its condition is met. The QRE says show it if: Q5 == 'Yes'</t>
+          <t>Prove Q6 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at least 10 characters; the answer must be at most 500 characters</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -2053,17 +2071,18 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>At Q6, type “xxxxxxxxxx”, then submit.</t>
+          <t>At Q6, type a 501-character answer, then submit.</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>1. Q6 IS shown on the page</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q6</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Shows / hides correctly</t>
+          <t>Answer rule accepts or rejects</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2094,12 +2113,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>TC-d6163f31ce</t>
+          <t>TC-5ba7c7d062</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Prove Q6 does NOT appear when its condition is not met. The QRE says show it if: Q5 == 'Yes'</t>
+          <t>Prove Q6 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a text question</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -2110,23 +2129,23 @@
 4. Q2 = Very poor
 5. Q3 = Very poor
 6. Q4 = Content relevance
-7. Q5 = No</t>
+7. Q5 = Yes</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>After submitting Q5, look for Q6 on the next page. Do not answer it.</t>
+          <t>At Q6, type nothing, then submit.</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>1. Q6 is NOT shown on the page
-2. the respondent carries on into the survey rather than being screened out or finished</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q6</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Shows / hides correctly</t>
+          <t>Blank answer is blocked</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2157,12 +2176,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>TC-1381ffa1c7</t>
+          <t>TC-ad86701f00</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Prove Q6 ACCEPTS an answer that obeys its rule. The QRE's rule is: the answer must be at least 10 characters; the answer must be at most 500 characters</t>
+          <t>Prove Q6 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at least 10 characters; the answer must be at most 500 characters</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -2178,7 +2197,7 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>At Q6, type “xxxxxxxxxx”, then submit.</t>
+          <t>At Q6, type a 500-character answer, then submit.</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -2219,7 +2238,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>TC-f70be2f9f4</t>
+          <t>TC-566303fa26</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -2240,13 +2259,12 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>At Q6, type a 501-character answer, then submit.</t>
+          <t>At Q6, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q6</t>
+          <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2282,7 +2300,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>TC-5ba7c7d062</t>
+          <t>TC-2587d31b15</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -2303,7 +2321,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>At Q6, type nothing, then submit.</t>
+          <t>At Q6, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -2329,13 +2347,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Q6</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Q6 | Please describe the main problem. | text | — | Show if: Q5 == 'Yes'
-Validate: {"min_length": 10, "max_length": 500}</t>
+          <t>Q7 | How likely are you to recommend this service? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Always show</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2345,326 +2362,15 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>TC-f854bec903</t>
+          <t>TC-6a0410fc63</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Q6's wording comes from Q5's answer: the earlier answer should appear in the wording</t>
+          <t>Prove the survey flows correctly at Q7: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>1. S1 = Yes
-2. S2 = Yes
-3. Q1 = In person
-4. Q2 = Very poor
-5. Q3 = Very poor
-6. Q4 = Content relevance
-7. Q5 = Yes</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>At Q6, type “xxxxxxxxxx”, then submit.</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>1. Q6's wording includes the words: Yes</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>Wording carried forward</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>Q6 | Please describe the main problem. | text | — | Show if: Q5 == 'Yes'
-Validate: {"min_length": 10, "max_length": 500}</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>TC-23513b235e</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>Q6 shown by its condition while also depending on Q5: both should hold at once</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>1. S1 = Yes
-2. S2 = Yes
-3. Q1 = In person
-4. Q2 = Very poor
-5. Q3 = Very poor
-6. Q4 = Content relevance
-7. Q5 = Yes</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>At Q6, type “xxxxxxxxxx”, then submit.</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>1. Q6 IS shown on the page
-2. Q6's wording includes the words: Yes</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>Two behaviours together</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>Q6 | Please describe the main problem. | text | — | Show if: Q5 == 'Yes'
-Validate: {"min_length": 10, "max_length": 500}</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>TC-ad86701f00</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>Prove Q6 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at least 10 characters; the answer must be at most 500 characters</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>1. S1 = Yes
-2. S2 = Yes
-3. Q1 = In person
-4. Q2 = Very poor
-5. Q3 = Very poor
-6. Q4 = Content relevance
-7. Q5 = Yes</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>At Q6, type a 500-character answer, then submit.</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>1. the survey ACCEPTS the answer and moves to the next page</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>Answer rule accepts or rejects</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>Q6 | Please describe the main problem. | text | — | Show if: Q5 == 'Yes'
-Validate: {"min_length": 10, "max_length": 500}</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>TC-566303fa26</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>Prove Q6 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at least 10 characters; the answer must be at most 500 characters</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>1. S1 = Yes
-2. S2 = Yes
-3. Q1 = In person
-4. Q2 = Very poor
-5. Q3 = Very poor
-6. Q4 = Content relevance
-7. Q5 = Yes</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>At Q6, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>1. the survey ACCEPTS the answer and moves to the next page</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>Answer rule accepts or rejects</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>Q6 | Please describe the main problem. | text | — | Show if: Q5 == 'Yes'
-Validate: {"min_length": 10, "max_length": 500}</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>TC-2587d31b15</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>Prove Q6 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a text question</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>1. S1 = Yes
-2. S2 = Yes
-3. Q1 = In person
-4. Q2 = Very poor
-5. Q3 = Very poor
-6. Q4 = Content relevance
-7. Q5 = Yes</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>At Q6, type 3 spaces and nothing else, then submit.</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q6</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>Blank answer is blocked</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Q7</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>Q7 | How likely are you to recommend this service? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Always show</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>TC-6a0410fc63</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>Prove the survey flows correctly at Q7: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -2677,58 +2383,58 @@
 9. Q7 = 0</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I37" s="3" t="inlineStr">
+      <c r="I32" s="3" t="inlineStr">
         <is>
           <t>1. Q7 IS shown on the page
 2. the next question shown is Q8</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Q7</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>Q7 | How likely are you to recommend this service? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Always show</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>TC-3af13688c6</t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>Prove Q7 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -2740,59 +2446,59 @@
 8. Q6 = xxxxxxxxxx</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>At Q7, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I38" s="3" t="inlineStr">
+      <c r="I33" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q7</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Q8</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>Q8 | What is the single most important improvement you would suggest? | text | — | Validate: {"max_length": 500}
 Optional</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>TC-6452a460af</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q8: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -2805,59 +2511,59 @@
 9. Q7 = 0</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr">
+      <c r="I34" s="3" t="inlineStr">
         <is>
           <t>1. Q8 IS shown on the page
 2. the respondent reaches the normal thank-you page</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Q8</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>Q8 | What is the single most important improvement you would suggest? | text | — | Validate: {"max_length": 500}
 Optional</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>TC-785a9414c4</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>Prove Q8 ACCEPTS an answer that obeys its rule. The QRE's rule is: the answer must be at most 500 characters</t>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -2870,58 +2576,58 @@
 9. Q7 = 0</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>At Q8, type “x”, then submit.</t>
         </is>
       </c>
-      <c r="I40" s="3" t="inlineStr">
+      <c r="I35" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>Q8</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>Q8 | What is the single most important improvement you would suggest? | text | — | Validate: {"max_length": 500}
 Optional</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>TC-12b005a4ef</t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t>Prove Q8 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at most 500 characters</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -2934,59 +2640,59 @@
 9. Q7 = 0</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr">
+      <c r="H36" s="3" t="inlineStr">
         <is>
           <t>At Q8, type a 501-character answer, then submit.</t>
         </is>
       </c>
-      <c r="I41" s="3" t="inlineStr">
+      <c r="I36" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q8</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>Q8</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>Q8 | What is the single most important improvement you would suggest? | text | — | Validate: {"max_length": 500}
 Optional</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>TC-35736daef1</t>
         </is>
       </c>
-      <c r="F42" s="3" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>Prove Q8 lets the respondent through with no answer, because the questionnaire marks it optional</t>
         </is>
       </c>
-      <c r="G42" s="3" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -2999,58 +2705,58 @@
 9. Q7 = 0</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr">
         <is>
           <t>At Q8, type nothing, then submit.</t>
         </is>
       </c>
-      <c r="I42" s="3" t="inlineStr">
+      <c r="I37" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="J37" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>Q8</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>Q8 | What is the single most important improvement you would suggest? | text | — | Validate: {"max_length": 500}
 Optional</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>TC-75945e73bd</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="F38" s="3" t="inlineStr">
         <is>
           <t>Prove Q8 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at most 500 characters</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="G38" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -3063,58 +2769,58 @@
 9. Q7 = 0</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr">
+      <c r="H38" s="3" t="inlineStr">
         <is>
           <t>At Q8, type a 500-character answer, then submit.</t>
         </is>
       </c>
-      <c r="I43" s="3" t="inlineStr">
+      <c r="I38" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>Q8</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>Q8 | What is the single most important improvement you would suggest? | text | — | Validate: {"max_length": 500}
 Optional</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>TC-4d9f269943</t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>Prove Q8 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at most 500 characters</t>
         </is>
       </c>
-      <c r="G44" s="3" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -3127,58 +2833,58 @@
 9. Q7 = 0</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr">
         <is>
           <t>At Q8, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
-      <c r="I44" s="3" t="inlineStr">
+      <c r="I39" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="J39" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Q8</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>Q8 | What is the single most important improvement you would suggest? | text | — | Validate: {"max_length": 500}
 Optional</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>TC-a7509385dc</t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="F40" s="3" t="inlineStr">
         <is>
           <t>Prove Q8 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a text question</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr">
+      <c r="G40" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -3191,53 +2897,53 @@
 9. Q7 = 0</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr">
+      <c r="H40" s="3" t="inlineStr">
         <is>
           <t>At Q8, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
-      <c r="I45" s="3" t="inlineStr">
+      <c r="I40" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>whole survey</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr"/>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr"/>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>TC-6b6c46c5df</t>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>Prove the survey finishes normally for a respondent who answers everything and triggers no screen-out</t>
         </is>
       </c>
-      <c r="G46" s="3" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -3250,22 +2956,22 @@
 9. Q7 = 0</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I46" s="3" t="inlineStr">
+      <c r="I41" s="3" t="inlineStr">
         <is>
           <t>1. the respondent reaches the normal thank-you page</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="J41" s="2" t="inlineStr">
         <is>
           <t>Survey ends in the right place</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
+      <c r="K41" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
